--- a/02_server_update/logs/UNKNOWN_202610_GAGAL_FALLBACK.xlsx
+++ b/02_server_update/logs/UNKNOWN_202610_GAGAL_FALLBACK.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -621,186 +621,6 @@
       <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Penyebab</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BTP JAK\PTLS\BOO_30-05\100.jpg</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PTLS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BOO_30-05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BTP JAK</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NO red guide detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BTP JAK\PTDS\CLT\100.jpg</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PTDS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CLT</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BTP JAK</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NO red guide detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BTP JAK\PTDS\CLT_03-05\100.jpg</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PTDS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CLT_03-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BTP JAK</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NO red guide detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BTP BD\CATUDAYA\BTT\0.jpg</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CATUDAYA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BTT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BTP BD</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NO red guide detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BTP BD\CATUDAYA\COS\100.jpg</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CATUDAYA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>COS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>BTP BD</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NO red guide detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BTP BD\CATUDAYA\RADIO_COS\0.jpg</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CATUDAYA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RADIO_COS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>BTP BD</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NO red guide detected</t>
         </is>
       </c>
     </row>
@@ -911,7 +731,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -931,7 +751,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
